--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1318,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2317,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2428,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2539,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2650,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2761,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2872,1240 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1235,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1354,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1415,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1473,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1490,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1534,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1592,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1601,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1653,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1783,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1823,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,12 +1933,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,10 +1974,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2045,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2234,12 +2282,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2267,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2275,10 +2323,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2378,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2933,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3663,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3774,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3821,7 +3885,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3870,7 +3934,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -3936,7 +4000,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4051,7 +4115,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4100,12 +4164,809 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>148.0</t>
         </is>
       </c>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1711,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1744,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1772,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1788,13 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1822,32 +1830,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1855,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,33 +1891,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2060,32 +2076,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2093,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,33 +2137,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2171,32 +2195,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2204,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,33 +2256,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2319,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq63，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2315,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2409,32 +2441,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2442,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,33 +2502,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2520,32 +2560,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2553,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,33 +2621,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2775,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2997,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3108,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3822,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4163,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4169,7 +4217,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4278,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4393,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4456,7 +4504,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4510,7 +4558,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4619,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4625,7 +4673,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4734,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4740,7 +4788,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4849,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4855,7 +4903,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4964,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4960,13 +5008,592 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2570,24 +2570,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2790,32 +2790,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,33 +2851,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3012,32 +3020,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3045,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,17 +3081,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3089,13 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -3267,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3311,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3311,13 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3489,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3600,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3711,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3822,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3933,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4048,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4217,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4528,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4558,7 +4582,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4788,7 +4812,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,7 +5103,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5194,7 +5218,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,7 +5333,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,7 +5448,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5563,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5588,12 +5612,349 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>151.0</t>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3139,32 +3139,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3200,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3216,13 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3260,24 +3268,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3369,32 +3377,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3402,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,33 +3438,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3480,32 +3496,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3513,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3557,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3557,13 +3577,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3591,32 +3615,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3624,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3648,33 +3676,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3957,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4241,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4301,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4302,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,37 +4362,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4420,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4417,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,10 +4461,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4528,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4582,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4610,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4643,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4667,17 +4723,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4687,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4812,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4912,7 +4968,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4927,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4988,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5042,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5157,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5272,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5387,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5502,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5617,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5789,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5954,7 +6010,697 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,18 +2751,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2881,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2996,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3821,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3932,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4523,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4676,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4699,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,12 +4752,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4781,32 +4785,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4814,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4838,17 +4846,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4858,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5011,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5044,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,17 +5080,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5088,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5126,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5159,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5183,17 +5199,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5203,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5241,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5274,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,37 +5318,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5356,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5389,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,17 +5437,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5433,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5586,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5619,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,17 +5671,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5663,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5701,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5734,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,33 +5790,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5931,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6010,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6125,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6240,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6355,7 +6391,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6470,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6585,7 +6621,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6593,22 +6629,22 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6641,12 +6677,12 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6660,47 +6696,725 @@
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr">
         <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr">
+      <c r="W54" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X53" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Z54" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
+      <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
         </is>
       </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>12/28</t>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2636,22 +2636,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,22 +3338,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3695,22 +3695,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5739,24 +5739,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5959,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,17 +6020,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6036,17 +6040,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6074,32 +6078,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6107,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,37 +6139,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -6222,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,37 +6258,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6304,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6337,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,17 +6377,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6381,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6419,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6452,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,37 +6496,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6682,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6736,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6851,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7023,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7269,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,7 +7380,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7409,12 +7429,587 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,18 +2037,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2532,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2651,7 +2655,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2885,7 +2889,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,14 +3223,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3348,12 +3352,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3476,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3591,7 +3595,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,12 +3709,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4266,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,14 +4746,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4985,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6050,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6207,24 +6211,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6234,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6407,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6445,12 +6449,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6554,32 +6558,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6587,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,17 +6619,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6631,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6669,32 +6677,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6702,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,37 +6738,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6784,32 +6796,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6817,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,17 +6857,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6861,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6915,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6932,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6940,10 +6956,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7010,32 +7038,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7043,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7067,33 +7099,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7208,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7549,7 +7585,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7659,12 +7695,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7779,7 +7815,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7876,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7889,12 +7925,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8009,7 +8045,582 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
           <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2411,13 +2411,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2540,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2605,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2645,17 +2649,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2720,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2760,17 +2764,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2893,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3004,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3119,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3238,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3347,17 +3351,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3595,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3664,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3714,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3814,7 +3818,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3825,7 +3829,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3940,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4520,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4994,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,14 +5222,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,14 +5460,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5939,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,17 +6286,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6768,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6806,24 +6810,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6924,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq57，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6948,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7010,7 +7014,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7048,24 +7052,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7075,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7157,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7190,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7214,17 +7222,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7234,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7272,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7305,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,17 +7341,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7349,13 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7416,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7460,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7460,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7498,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7531,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,17 +7579,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7575,17 +7599,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7613,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -7646,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7670,17 +7698,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7690,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7815,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7930,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7991,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8045,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8160,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8275,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8390,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8505,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8615,12 +8643,575 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,14 +1787,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,14 +3465,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3584,22 +3584,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3708,17 +3708,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7409,24 +7409,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7528,24 +7528,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7756,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7789,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7817,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7833,12 +7837,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7871,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7904,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,17 +7936,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7948,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7986,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8019,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,37 +8055,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8101,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8134,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,17 +8174,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8178,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8364,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8479,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8709,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8820,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8874,7 +8890,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9046,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9104,22 +9120,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9152,12 +9168,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9201,17 +9217,1052 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="AC74" s="2" t="inlineStr">
+      <c r="AC75" s="2" t="inlineStr">
         <is>
           <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,12 +6767,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8004,24 +8004,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8123,24 +8123,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8232,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8265,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,37 +8293,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8347,32 +8351,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8380,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,17 +8412,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8424,17 +8432,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8462,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8495,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,37 +8531,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8610,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8634,37 +8650,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8708,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq33推进至seq44，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8725,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8733,10 +8749,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq31映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8803,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8836,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8860,17 +8892,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8880,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9173,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9227,7 +9259,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9403,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9457,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9572,7 +9604,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9687,7 +9719,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9863,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9978,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10093,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10147,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10240,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10257,12 +10289,817 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,22 +5222,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,14 +8427,14 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -8480,24 +8480,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq33推进至seq44，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq33推进至seq59，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -8841,24 +8841,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8907,22 +8907,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       <c r="AB72" s="2" t="inlineStr"/>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9172,32 +9172,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9205,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,17 +9233,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9249,17 +9253,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -9287,32 +9291,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9320,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9344,17 +9352,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9364,17 +9372,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9489,7 +9497,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9589,7 +9597,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9604,7 +9612,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9719,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9834,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9949,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10064,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10179,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10294,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10639,7 +10647,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10754,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10869,7 +10877,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10979,12 +10987,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11099,7 +11107,685 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57601A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3108,14 +3108,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>140.7</t>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,22 +3465,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>156.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,14 +5460,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>140.7</t>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,22 +6400,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,17 +6643,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,14 +7832,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>140.7</t>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>156.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9367,14 +9367,14 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -9410,32 +9410,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9443,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9467,37 +9471,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9525,32 +9529,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9558,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9582,17 +9590,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9602,17 +9610,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -9640,32 +9648,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9673,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9697,37 +9709,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9755,32 +9767,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9788,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,37 +9828,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9870,32 +9886,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9903,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9927,17 +9947,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9947,17 +9967,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -9985,32 +10005,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10018,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10042,37 +10066,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10100,32 +10124,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10133,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,17 +10185,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10177,17 +10205,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10215,32 +10243,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10248,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10272,17 +10304,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10292,17 +10324,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>156.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10593,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10708,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10762,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10877,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10992,7 +11024,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11053,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11279,7 +11311,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11333,7 +11365,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11505,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11616,7 +11648,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11670,7 +11702,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11678,22 +11710,22 @@
       <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11726,12 +11758,12 @@
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11745,47 +11777,852 @@
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr">
+      <c r="W97" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X96" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z96" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA96" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB96" s="2" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
-      </c>
-      <c r="AC96" s="2" t="inlineStr">
-        <is>
-          <t>7/31</t>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>4/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>149.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>145.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>21/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3823,13 +3823,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4049,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6004,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6242,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6772,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,12 +7246,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7436,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8031,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,12 +8079,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8204,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8551,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8868,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9094,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,13 +9142,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9447,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9501,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9685,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9804,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9858,7 +9866,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10215,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10243,36 +10251,32 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10280,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10304,17 +10308,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10324,12 +10328,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10395,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10434,7 +10438,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10477,32 +10481,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10510,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10534,17 +10542,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10554,12 +10562,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10592,32 +10600,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10625,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,17 +10661,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10669,17 +10681,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10707,32 +10719,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10740,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10780,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10784,17 +10800,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10822,32 +10838,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -10855,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10879,17 +10899,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10899,17 +10919,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10937,32 +10957,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10970,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +11018,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,17 +11038,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11200,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11239,7 +11263,7 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11426,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11504,32 +11528,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11537,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11561,17 +11589,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11581,13 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11680,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11702,7 +11734,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11795,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11878,7 +11910,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11993,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12108,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12223,7 +12255,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12277,7 +12309,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12370,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12392,7 +12424,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12485,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12568,7 +12600,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12626,6 +12658,232 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,17 +4164,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9618,17 +9618,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -11417,32 +11417,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>17:41</t>
@@ -11450,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11474,17 +11478,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11494,13 +11498,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB93" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11538,12 +11546,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -11565,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11614,7 +11622,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11647,32 +11655,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11680,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11704,17 +11716,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11724,17 +11736,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11762,12 +11774,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11795,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11803,10 +11815,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11849,7 +11877,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11905,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11910,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11934,17 +11966,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11954,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11992,32 +12024,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12025,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12049,17 +12085,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12069,17 +12105,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12176,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12255,7 +12291,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12309,7 +12345,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12424,7 +12460,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12521,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12539,7 +12575,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -12600,7 +12636,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12654,7 +12690,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12805,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12866,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">

--- a/data/export/2026-10-30-浦东35路.xlsx
+++ b/data/export/2026-10-30-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2883,17 +2883,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9499,17 +9499,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9856,17 +9856,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10094,17 +10094,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12258,32 +12258,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12291,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12315,17 +12319,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12335,17 +12339,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12373,32 +12377,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12406,7 +12414,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12430,17 +12438,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12450,17 +12458,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12488,32 +12496,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12521,7 +12533,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12545,17 +12557,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12565,17 +12577,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12615,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12636,7 +12652,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12660,17 +12676,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12680,17 +12696,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12821,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
